--- a/outputs/excel/model_inference_tables.xlsx
+++ b/outputs/excel/model_inference_tables.xlsx
@@ -15,14 +15,15 @@
     <sheet name="Holt_linear" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="HoltWinters_additive" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="HoltWinters_multiplicative" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MLR_with_lead" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="MLR_no_lead" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="AR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ARMA" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ARIMA" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SARIMA" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SARIMAX_with_lead" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="SARIMAX_no_lead" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Trend_Dummy_Reg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MLR_with_lead" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MLR_no_lead" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="AR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ARMA" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ARIMA" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SARIMA" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SARIMAX_with_lead" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SARIMAX_no_lead" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -188,7 +189,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -218,6 +219,36 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="13544550" cy="3295650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
@@ -242,7 +273,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -368,7 +399,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -398,7 +429,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -428,7 +459,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -458,7 +489,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -488,7 +519,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="13544550" cy="3295650"/>
@@ -801,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +943,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -926,45 +957,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7394.310784885945</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="F2" t="n">
-        <v>11220.91902220608</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="G2" t="n">
-        <v>28.14532924096643</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="H2" t="n">
-        <v>90.32258064516128</v>
+        <v>93.54838709677419</v>
       </c>
       <c r="I2" t="n">
-        <v>54.02949391845218</v>
+        <v>224.886106476582</v>
       </c>
       <c r="J2" t="n">
-        <v>107.469050157937</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6314847106965941</v>
+        <v>2.330839206710618e-19</v>
       </c>
       <c r="M2" t="n">
-        <v>1.588424543666641e-138</v>
+        <v>1.331886348383204e-27</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>yes (oracle)</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>dec_surge_2023 dummy regressor</t>
+          <t>target adjusted by surge multiplier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SARIMAX(0, 1, 2)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -986,72 +1017,72 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HoltWinters_multiplicative</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ETS(error=M, trend=A, seasonal=M, m=7)</t>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>log</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9891.199250710853</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="F3" t="n">
-        <v>15025.08513891423</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="G3" t="n">
-        <v>30.49396396858601</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="H3" t="n">
-        <v>80.64516129032258</v>
+        <v>90.32258064516128</v>
       </c>
       <c r="I3" t="n">
-        <v>6711.819649885386</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="J3" t="n">
-        <v>6761.480727979966</v>
+        <v>107.469050157937</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1894301486753809</v>
+        <v>0.6314847106965941</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.588424543666641e-138</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes (oracle)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>target adjusted by surge multiplier</t>
+          <t>dec_surge_2023 dummy regressor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ETS(error=M, trend=A, seasonal=M, m=7)</t>
+          <t>SARIMAX(0, 1, 2)(1, 0, 0, 7) trend=n + exog on log demand</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1060,45 +1091,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HoltWinters_multiplicative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
+          <t>ETS(error=M, trend=A, seasonal=M, m=7)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9108.629861189735</v>
+        <v>9891.199250710853</v>
       </c>
       <c r="F4" t="n">
-        <v>12754.97559384381</v>
+        <v>15025.08513891423</v>
       </c>
       <c r="G4" t="n">
-        <v>31.05750751419404</v>
+        <v>30.49396396858601</v>
       </c>
       <c r="H4" t="n">
-        <v>77.41935483870968</v>
+        <v>80.64516129032258</v>
       </c>
       <c r="I4" t="n">
-        <v>133.8675397506205</v>
+        <v>6711.819649885386</v>
       </c>
       <c r="J4" t="n">
-        <v>149.0639103684626</v>
+        <v>6761.480727979966</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1143517866357309</v>
+        <v>0.1894301486753809</v>
       </c>
       <c r="M4" t="n">
-        <v>9.735748956188667e-82</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1112,20 +1143,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 1)(1, 1, 1, 7) trend=t on log demand</t>
+          <t>ETS(error=M, trend=A, seasonal=M, m=7)</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1134,45 +1165,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HoltWinters_additive</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=A, seasonal=A, m=7)</t>
+          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>log</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9646.430988111515</v>
+        <v>9108.629861189735</v>
       </c>
       <c r="F5" t="n">
-        <v>13217.1650755761</v>
+        <v>12754.97559384381</v>
       </c>
       <c r="G5" t="n">
-        <v>33.63072605141772</v>
+        <v>31.05750751419404</v>
       </c>
       <c r="H5" t="n">
-        <v>80.64516129032258</v>
+        <v>77.41935483870968</v>
       </c>
       <c r="I5" t="n">
-        <v>6923.603883059114</v>
+        <v>133.8675397506205</v>
       </c>
       <c r="J5" t="n">
-        <v>6973.264961153694</v>
+        <v>149.0639103684626</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>4.227114249027085e-05</v>
+        <v>0.1143517866357309</v>
       </c>
       <c r="M5" t="n">
-        <v>4.233725292740843e-311</v>
+        <v>9.735748956188667e-82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1186,7 +1217,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=A, seasonal=A, m=7)</t>
+          <t>SARIMA(1, 0, 1)(1, 1, 1, 7) trend=t on log demand</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1196,10 +1227,10 @@
         <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1208,45 +1239,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>HoltWinters_additive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>ETS(error=A, trend=A, seasonal=A, m=7)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8836.438892027803</v>
+        <v>9646.430988111515</v>
       </c>
       <c r="F6" t="n">
-        <v>11839.66568147391</v>
+        <v>13217.1650755761</v>
       </c>
       <c r="G6" t="n">
-        <v>34.32789868612172</v>
+        <v>33.63072605141772</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>80.64516129032258</v>
       </c>
       <c r="I6" t="n">
-        <v>98.87841004798804</v>
+        <v>6923.603883059114</v>
       </c>
       <c r="J6" t="n">
-        <v>144.4675219015143</v>
+        <v>6973.264961153694</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03431889047521499</v>
+        <v>4.227114249027085e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.329793091831646e-63</v>
+        <v>4.233725292740843e-311</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1255,25 +1286,25 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>dec_surge_2023 dummy regressor</t>
+          <t>target adjusted by surge multiplier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>ETS(error=A, trend=A, seasonal=A, m=7)</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>3.666666666666667</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1282,12 +1313,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1296,35 +1327,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9167.306312588355</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="F7" t="n">
-        <v>12516.99275536766</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="G7" t="n">
-        <v>36.28102722777211</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>16.2116785128743</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="J7" t="n">
-        <v>65.59988302086113</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02353916574718243</v>
+        <v>0.03431889047521499</v>
       </c>
       <c r="M7" t="n">
-        <v>1.69046453687632e-186</v>
+        <v>2.329793091831646e-63</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>yes (oracle)</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1334,7 +1365,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1344,10 +1375,10 @@
         <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -1356,12 +1387,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1370,35 +1401,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7552.243223539159</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="F8" t="n">
-        <v>9283.570749349237</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="G8" t="n">
-        <v>37.29118892550915</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="H8" t="n">
-        <v>93.54838709677419</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>127.2747055697288</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="J8" t="n">
-        <v>176.8971506492504</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4428764196275751</v>
+        <v>0.02353916574718243</v>
       </c>
       <c r="M8" t="n">
-        <v>1.345528170430006e-72</v>
+        <v>1.69046453687632e-186</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes (oracle)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1408,20 +1439,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SARIMAX(0, 1, 2)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1430,45 +1461,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>SARIMAX_no_lead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=N, seasonal=N)</t>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>log</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9957.081624484823</v>
+        <v>7552.243223539159</v>
       </c>
       <c r="F9" t="n">
-        <v>13678.53513599809</v>
+        <v>9283.570749349237</v>
       </c>
       <c r="G9" t="n">
-        <v>37.64408034366238</v>
+        <v>37.29118892550915</v>
       </c>
       <c r="H9" t="n">
-        <v>80.64516129032258</v>
+        <v>93.54838709677419</v>
       </c>
       <c r="I9" t="n">
-        <v>7149.630480567437</v>
+        <v>127.2747055697288</v>
       </c>
       <c r="J9" t="n">
-        <v>7161.090729358494</v>
+        <v>176.8971506492504</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
-        <v>1.734760530539618e-110</v>
+        <v>0.4428764196275751</v>
       </c>
       <c r="M9" t="n">
-        <v>5.49396981982565e-47</v>
+        <v>1.345528170430006e-72</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1477,25 +1508,25 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>target adjusted by surge multiplier</t>
+          <t>dec_surge_2023 dummy regressor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=N, seasonal=N)</t>
+          <t>SARIMAX(0, 1, 2)(1, 0, 0, 7) trend=n + exog on log demand</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1504,45 +1535,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ETS(error=A, trend=N, seasonal=N)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13265.28655765335</v>
+        <v>9957.081624484823</v>
       </c>
       <c r="F10" t="n">
-        <v>18455.55922268183</v>
+        <v>13678.53513599809</v>
       </c>
       <c r="G10" t="n">
-        <v>45.91726426082142</v>
+        <v>37.64408034366238</v>
       </c>
       <c r="H10" t="n">
-        <v>77.41935483870968</v>
+        <v>80.64516129032258</v>
       </c>
       <c r="I10" t="n">
-        <v>181.530354011536</v>
+        <v>7149.630480567437</v>
       </c>
       <c r="J10" t="n">
-        <v>219.7014656111681</v>
+        <v>7161.090729358494</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001236689819004854</v>
+        <v>1.734760530539618e-110</v>
       </c>
       <c r="M10" t="n">
-        <v>3.464139302452156e-32</v>
+        <v>5.49396981982565e-47</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1556,20 +1587,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 0) trend=t on log demand</t>
+          <t>ETS(error=A, trend=N, seasonal=N)</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>10.33333333333333</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1578,12 +1609,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1592,31 +1623,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13317.70475627446</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="F11" t="n">
-        <v>17853.90132441626</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="G11" t="n">
-        <v>48.08128422960952</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="H11" t="n">
         <v>77.41935483870968</v>
       </c>
       <c r="I11" t="n">
-        <v>179.3767394101604</v>
+        <v>181.530354011536</v>
       </c>
       <c r="J11" t="n">
-        <v>213.5685733003051</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002187027907619822</v>
+        <v>0.001236689819004854</v>
       </c>
       <c r="M11" t="n">
-        <v>6.24723369018292e-95</v>
+        <v>3.464139302452156e-32</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1630,20 +1661,20 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>ARIMA(7, 1, 0) trend=t on log demand</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>10.33333333333333</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1652,45 +1683,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Holt_linear</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=A, seasonal=N)</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>log</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11588.47236653361</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="F12" t="n">
-        <v>13361.08930363182</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="G12" t="n">
-        <v>52.74839742105731</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="H12" t="n">
-        <v>96.7741935483871</v>
+        <v>77.41935483870968</v>
       </c>
       <c r="I12" t="n">
-        <v>7178.322992676578</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="J12" t="n">
-        <v>7197.42340732834</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.241932363754178e-109</v>
+        <v>0.0002187027907619822</v>
       </c>
       <c r="M12" t="n">
-        <v>1.860793262826696e-28</v>
+        <v>6.24723369018292e-95</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1704,20 +1735,20 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ETS(error=A, trend=A, seasonal=N)</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>9</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -1726,45 +1757,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>Holt_linear</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ETS(error=A, trend=A, seasonal=N)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14737.37333953242</v>
+        <v>11588.47236653361</v>
       </c>
       <c r="F13" t="n">
-        <v>18358.33359956474</v>
+        <v>13361.08930363182</v>
       </c>
       <c r="G13" t="n">
-        <v>57.57383391940481</v>
+        <v>52.74839742105731</v>
       </c>
       <c r="H13" t="n">
-        <v>74.19354838709677</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="I13" t="n">
-        <v>165.3889470634342</v>
+        <v>7178.322992676578</v>
       </c>
       <c r="J13" t="n">
-        <v>210.9780589169605</v>
+        <v>7197.42340732834</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>8.8471217794124e-05</v>
+        <v>1.241932363754178e-109</v>
       </c>
       <c r="M13" t="n">
-        <v>7.854027374969633e-50</v>
+        <v>1.860793262826696e-28</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1778,20 +1809,94 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ETS(error=A, trend=A, seasonal=N)</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ARMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14737.37333953242</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18358.33359956474</v>
+      </c>
+      <c r="G14" t="n">
+        <v>57.57383391940481</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.19354838709677</v>
+      </c>
+      <c r="I14" t="n">
+        <v>165.3889470634342</v>
+      </c>
+      <c r="J14" t="n">
+        <v>210.9780589169605</v>
+      </c>
+      <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="T13" t="n">
-        <v>11.66666666666667</v>
+      <c r="L14" t="n">
+        <v>8.8471217794124e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7.854027374969633e-50</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>target adjusted by surge multiplier</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>13</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12.66666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1800,6 +1905,850 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>MLR_with_lead — inference table (validation metrics: Jan 2024, multi-step)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>parameter/order</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>coefficient_or_component</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>std_error</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>p_value_or_significance</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.696240178688386</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7168212747589217</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K3" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))). USES REALISED LEAD TIME for forecast dates (information not available in advance) - optimistic/oracle scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lag1_log_demand</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1967654320199931</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09784578666994671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0443 *</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K4" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>lag7_log_demand</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3179456114877093</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07934494859968066</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0001 ***</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H5" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dow_Tue</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.009367935580455927</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05787834148776607</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.8714 ns</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H6" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K6" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dow_Wed</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.149087255613652</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09451253528506465</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.1147 ns</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H7" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dow_Thu</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2862472886603507</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09708820071458177</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.0032 **</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H8" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dow_Fri</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1761451594528244</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.05964930279107389</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0031 **</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H9" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dow_Sat</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6093423269863116</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1574562723983261</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0001 ***</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K10" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dow_Sun</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3171253249757077</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09816353733158333</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0012 **</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H11" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K11" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>is_holiday</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.01264020421706977</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.05017640757805472</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.8011 ns</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H12" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K12" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dec_surge_2023</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1840496799769273</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1334841640408609</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.1680 ns</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H13" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K13" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>booknow_missing</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03805524728166586</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03200316502979435</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.2344 ns</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H14" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K14" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MLR_with_lead</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lead_100h</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3562186524960662</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1698309457411886</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0360 *</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>16.2116785128743</v>
+      </c>
+      <c r="H15" t="n">
+        <v>65.59988302086113</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9167.306312588355</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12516.99275536766</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Residual diagnostics (in-sample, train)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ljung-Box lag 7</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9.206945207311039</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1010890987915266</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>residuals white noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ljung-Box lag 14</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>23.53133842338016</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02353916574718243</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>autocorrelation left</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ljung-Box lag 21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>29.74160845500177</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.05518036044962926</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>residuals white noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jarque-Bera normality</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>855.5116478636742</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.69046453687632e-186</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>non-normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shapiro-Wilk normality</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.8951222792615157</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.635095636036399e-14</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>non-normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.6997142241938138</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>excess kurtosis</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7.762771989011615</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Residual plot, ACF and Q-Q</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2599,7 +3548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3530,7 +4479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4689,7 +5638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5650,7 +6599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6457,7 +7406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7704,7 +8653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8913,7 +9862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9094,124 +10043,155 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31624.26641596929</v>
+        <v>4886.65863535256</v>
       </c>
       <c r="D6" t="n">
-        <v>37632.62292155452</v>
+        <v>6499.979152024692</v>
       </c>
       <c r="E6" t="n">
-        <v>167.1342860093954</v>
+        <v>20.80566474883626</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>48.08128422960952</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="H6" t="n">
-        <v>17853.90132441626</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="I6" t="n">
-        <v>13317.70475627446</v>
+        <v>7000.529711986843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARMA(7,1) + const on Δ7 log demand  [= ARIMA(7,0,1)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30429.6201091783</v>
+        <v>31624.26641596929</v>
       </c>
       <c r="D7" t="n">
-        <v>37516.34239023783</v>
+        <v>37632.62292155452</v>
       </c>
       <c r="E7" t="n">
-        <v>162.4809718209972</v>
+        <v>167.1342860093954</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="H7" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="I7" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,1) + const on Δ7 log demand  [= ARIMA(7,0,1)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30510.30157923356</v>
+        <v>30429.6201091783</v>
       </c>
       <c r="D8" t="n">
-        <v>35101.83722837154</v>
+        <v>37516.34239023783</v>
       </c>
       <c r="E8" t="n">
-        <v>165.9947247814602</v>
+        <v>162.4809718209972</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="H8" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="I8" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 2)(1, 1, 1, 7) trend=t on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14176.8638853558</v>
+        <v>30510.30157923356</v>
       </c>
       <c r="D9" t="n">
-        <v>17009.47182289654</v>
+        <v>35101.83722837154</v>
       </c>
       <c r="E9" t="n">
-        <v>71.47604514454883</v>
+        <v>165.9947247814602</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
+        <v>45.91726426082142</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18455.55922268183</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13265.28655765335</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SARIMA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SARIMA(1, 0, 2)(1, 1, 1, 7) trend=t on log demand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14176.8638853558</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17009.47182289654</v>
+      </c>
+      <c r="E10" t="n">
+        <v>71.47604514454883</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
         <v>31.05750751419404</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>12754.97559384381</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>9108.629861189735</v>
       </c>
     </row>
@@ -9342,7 +10322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10736,12 +11716,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10750,10 +11730,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.696240178688386</v>
+        <v>9.300356922356313</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7168212747589217</v>
+        <v>0.07428650903424695</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -10761,331 +11741,331 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H32" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I32" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J32" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K32" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))). USES REALISED LEAD TIME for forecast dates (information not available in advance) - optimistic/oracle scenario.</t>
+          <t>Trend + seasonal-dummy regression on log demand (exp(coef) = multiplier vs Monday). No lags, so residual autocorrelation is expected; HAC(7) standard errors. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lag1_log_demand</t>
+          <t>trend_month</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1967654320199931</v>
+        <v>0.02960393764688295</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09784578666994671</v>
+        <v>0.00998812775251692</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0443 *</t>
+          <t>0.0030 **</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H33" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I33" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J33" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K33" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lag7_log_demand</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3179456114877093</v>
+        <v>-0.3244542000400762</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07934494859968066</v>
+        <v>0.0476166389251341</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.0001 ***</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H34" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I34" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J34" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K34" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dow_Tue</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.009367935580455927</v>
+        <v>-0.2319086230854109</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05787834148776607</v>
+        <v>0.07086703161902613</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.8714 ns</t>
+          <t>0.0011 **</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H35" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I35" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J35" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K35" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dow_Wed</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.149087255613652</v>
+        <v>0.037557561004528</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09451253528506465</v>
+        <v>0.07475173495063558</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.1147 ns</t>
+          <t>0.6154 ns</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H36" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I36" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J36" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K36" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dow_Thu</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2862472886603507</v>
+        <v>-0.003116878632527642</v>
       </c>
       <c r="E37" t="n">
-        <v>0.09708820071458177</v>
+        <v>0.07208266541889143</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.0032 **</t>
+          <t>0.9655 ns</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H37" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I37" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J37" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K37" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dow_Fri</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1761451594528244</v>
+        <v>0.7235793767118635</v>
       </c>
       <c r="E38" t="n">
-        <v>0.05964930279107389</v>
+        <v>0.09320822091908157</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.0031 **</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H38" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I38" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J38" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K38" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dow_Sat</t>
+          <t>dow_Sun</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6093423269863116</v>
+        <v>0.676017892445303</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1574562723983261</v>
+        <v>0.06105984446324666</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.0001 ***</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H39" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I39" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J39" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K39" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -11102,18 +12082,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dow_Sun</t>
+          <t>const</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.3171253249757077</v>
+        <v>3.696240178688386</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09816353733158333</v>
+        <v>0.7168212747589217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.0012 **</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -11131,7 +12111,11 @@
       <c r="K40" t="n">
         <v>36.28102722777211</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))). USES REALISED LEAD TIME for forecast dates (information not available in advance) - optimistic/oracle scenario.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11146,18 +12130,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>is_holiday</t>
+          <t>lag1_log_demand</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-0.01264020421706977</v>
+        <v>0.1967654320199931</v>
       </c>
       <c r="E41" t="n">
-        <v>0.05017640757805472</v>
+        <v>0.09784578666994671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.8011 ns</t>
+          <t>0.0443 *</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -11190,18 +12174,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dec_surge_2023</t>
+          <t>lag7_log_demand</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1840496799769273</v>
+        <v>0.3179456114877093</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1334841640408609</v>
+        <v>0.07934494859968066</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.1680 ns</t>
+          <t>0.0001 ***</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -11234,18 +12218,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>booknow_missing</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.03805524728166586</v>
+        <v>0.009367935580455927</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03200316502979435</v>
+        <v>0.05787834148776607</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2344 ns</t>
+          <t>0.8714 ns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -11278,18 +12262,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>lead_100h</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.3562186524960662</v>
+        <v>0.149087255613652</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1698309457411886</v>
+        <v>0.09451253528506465</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.0360 *</t>
+          <t>0.1147 ns</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -11312,356 +12296,352 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.721451625414947</v>
+        <v>0.2862472886603507</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6623401801732882</v>
+        <v>0.09708820071458177</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0032 **</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H45" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I45" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J45" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K45" t="n">
-        <v>34.32789868612172</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))).</t>
-        </is>
-      </c>
+        <v>36.28102722777211</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>lag1_log_demand</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.3307049784836344</v>
+        <v>0.1761451594528244</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08230049643124769</v>
+        <v>0.05964930279107389</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.0001 ***</t>
+          <t>0.0031 **</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H46" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I46" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J46" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K46" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>lag7_log_demand</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.3558654857635506</v>
+        <v>0.6093423269863116</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09560923493506153</v>
+        <v>0.1574562723983261</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.0002 ***</t>
+          <t>0.0001 ***</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H47" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I47" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J47" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K47" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dow_Tue</t>
+          <t>dow_Sun</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.05008074311541695</v>
+        <v>0.3171253249757077</v>
       </c>
       <c r="E48" t="n">
-        <v>0.06726187218038884</v>
+        <v>0.09816353733158333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.4565 ns</t>
+          <t>0.0012 **</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H48" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I48" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J48" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K48" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dow_Wed</t>
+          <t>is_holiday</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2251156423366464</v>
+        <v>-0.01264020421706977</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1014523523845049</v>
+        <v>0.05017640757805472</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.0265 *</t>
+          <t>0.8011 ns</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H49" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I49" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J49" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K49" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dow_Thu</t>
+          <t>dec_surge_2023</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.3701006415457713</v>
+        <v>0.1840496799769273</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1028642204571042</v>
+        <v>0.1334841640408609</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.0003 ***</t>
+          <t>0.1680 ns</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H50" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I50" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J50" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K50" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dow_Fri</t>
+          <t>booknow_missing</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2530805555253318</v>
+        <v>0.03805524728166586</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0731135744862368</v>
+        <v>0.03200316502979435</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.0005 ***</t>
+          <t>0.2344 ns</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H51" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I51" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J51" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K51" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MLR_no_lead</t>
+          <t>MLR_with_lead</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dow_Sat</t>
+          <t>lead_100h</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.7373486277454893</v>
+        <v>0.3562186524960662</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1677255464589885</v>
+        <v>0.1698309457411886</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0360 *</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>98.87841004798804</v>
+        <v>16.2116785128743</v>
       </c>
       <c r="H52" t="n">
-        <v>144.4675219015143</v>
+        <v>65.59988302086113</v>
       </c>
       <c r="I52" t="n">
-        <v>8836.438892027803</v>
+        <v>9167.306312588355</v>
       </c>
       <c r="J52" t="n">
-        <v>11839.66568147391</v>
+        <v>12516.99275536766</v>
       </c>
       <c r="K52" t="n">
-        <v>34.32789868612172</v>
+        <v>36.28102722777211</v>
       </c>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -11678,14 +12658,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dow_Sun</t>
+          <t>const</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.4272320593794858</v>
+        <v>2.721451625414947</v>
       </c>
       <c r="E53" t="n">
-        <v>0.08899343218808142</v>
+        <v>0.6623401801732882</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -11707,7 +12687,11 @@
       <c r="K53" t="n">
         <v>34.32789868612172</v>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -11722,18 +12706,18 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>is_holiday</t>
+          <t>lag1_log_demand</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.03725084505095579</v>
+        <v>0.3307049784836344</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05877377625058394</v>
+        <v>0.08230049643124769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.5262 ns</t>
+          <t>0.0001 ***</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11766,18 +12750,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dec_surge_2023</t>
+          <t>lag7_log_demand</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.3760721809688986</v>
+        <v>0.3558654857635506</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1181908552064788</v>
+        <v>0.09560923493506153</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.0015 **</t>
+          <t>0.0002 ***</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11810,18 +12794,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>booknow_missing</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-0.003705005710507528</v>
+        <v>0.05008074311541695</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02949312820703615</v>
+        <v>0.06726187218038884</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9000 ns</t>
+          <t>0.4565 ns</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11844,356 +12828,352 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>drift (log/day)</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.00133344252899014</v>
+        <v>0.2251156423366464</v>
       </c>
       <c r="E57" t="n">
-        <v>0.003842439159266953</v>
+        <v>0.1014523523845049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.7286 ns</t>
+          <t>0.0265 *</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H57" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I57" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J57" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K57" t="n">
-        <v>48.08128422960952</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Stationary series = seasonal difference of log demand (ADF &amp; KPSS agree, Phase 2). Order chosen by AIC over p≤7, q=0 (7 candidates). 'drift' is the constant of the Δ7 equation expressed per day. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
-        </is>
-      </c>
+        <v>34.32789868612172</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.3759232446072708</v>
+        <v>0.3701006415457713</v>
       </c>
       <c r="E58" t="n">
-        <v>0.03879223805039706</v>
+        <v>0.1028642204571042</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0003 ***</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H58" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I58" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J58" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K58" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ar.L2</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.05442818534092655</v>
+        <v>0.2530805555253318</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04787302709123251</v>
+        <v>0.0731135744862368</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.2556 ns</t>
+          <t>0.0005 ***</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H59" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I59" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J59" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K59" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ar.L3</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.03066244070221623</v>
+        <v>0.7373486277454893</v>
       </c>
       <c r="E60" t="n">
-        <v>0.06143163650210003</v>
+        <v>0.1677255464589885</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.6177 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H60" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I60" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J60" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K60" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ar.L4</t>
+          <t>dow_Sun</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.03010711256932699</v>
+        <v>0.4272320593794858</v>
       </c>
       <c r="E61" t="n">
-        <v>0.05471572487699053</v>
+        <v>0.08899343218808142</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.5822 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H61" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I61" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J61" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K61" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ar.L5</t>
+          <t>is_holiday</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.06773444830553302</v>
+        <v>-0.03725084505095579</v>
       </c>
       <c r="E62" t="n">
-        <v>0.06657906318023601</v>
+        <v>0.05877377625058394</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.3090 ns</t>
+          <t>0.5262 ns</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H62" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I62" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J62" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K62" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ar.L6</t>
+          <t>dec_surge_2023</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1032258589352957</v>
+        <v>0.3760721809688986</v>
       </c>
       <c r="E63" t="n">
-        <v>0.06694697970197505</v>
+        <v>0.1181908552064788</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.1231 ns</t>
+          <t>0.0015 **</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H63" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I63" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J63" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K63" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MLR_no_lead</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
+          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ar.L7</t>
+          <t>booknow_missing</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-0.3577693040221521</v>
+        <v>-0.003705005710507528</v>
       </c>
       <c r="E64" t="n">
-        <v>0.046042162151903</v>
+        <v>0.02949312820703615</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.9000 ns</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>179.3767394101604</v>
+        <v>98.87841004798804</v>
       </c>
       <c r="H64" t="n">
-        <v>213.5685733003051</v>
+        <v>144.4675219015143</v>
       </c>
       <c r="I64" t="n">
-        <v>13317.70475627446</v>
+        <v>8836.438892027803</v>
       </c>
       <c r="J64" t="n">
-        <v>17853.90132441626</v>
+        <v>11839.66568147391</v>
       </c>
       <c r="K64" t="n">
-        <v>48.08128422960952</v>
+        <v>34.32789868612172</v>
       </c>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -12210,18 +13190,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>drift (log/day)</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.09513254441900669</v>
+        <v>0.00133344252899014</v>
       </c>
       <c r="E65" t="n">
-        <v>0.004507880150999792</v>
+        <v>0.003842439159266953</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.7286 ns</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -12239,341 +13219,341 @@
       <c r="K65" t="n">
         <v>48.08128422960952</v>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Stationary series = seasonal difference of log demand (ADF &amp; KPSS agree, Phase 2). Order chosen by AIC over p≤7, q=0 (7 candidates). 'drift' is the constant of the Δ7 equation expressed per day. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>drift (log/day)</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.001674918607212042</v>
+        <v>0.3759232446072708</v>
       </c>
       <c r="E66" t="n">
-        <v>0.00236816292397168</v>
+        <v>0.03879223805039706</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.4794 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H66" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I66" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J66" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K66" t="n">
-        <v>57.57383391940481</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Stationary series = seasonal difference of log demand (ADF &amp; KPSS agree, Phase 2). Order chosen by AIC over p≤7, q≤3 (31 candidates). 'drift' is the constant of the Δ7 equation expressed per day. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
-        </is>
-      </c>
+        <v>48.08128422960952</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>ar.L2</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-0.1268547428162264</v>
+        <v>0.05442818534092655</v>
       </c>
       <c r="E67" t="n">
-        <v>0.116969457387242</v>
+        <v>0.04787302709123251</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.2781 ns</t>
+          <t>0.2556 ns</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H67" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I67" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J67" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K67" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ar.L2</t>
+          <t>ar.L3</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.7511835494260695</v>
+        <v>0.03066244070221623</v>
       </c>
       <c r="E68" t="n">
-        <v>0.08435763121964718</v>
+        <v>0.06143163650210003</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.6177 ns</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H68" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I68" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J68" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K68" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ar.L3</t>
+          <t>ar.L4</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.2779492326884617</v>
+        <v>0.03010711256932699</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1056935859509285</v>
+        <v>0.05471572487699053</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.0085 **</t>
+          <t>0.5822 ns</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H69" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I69" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J69" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K69" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ar.L4</t>
+          <t>ar.L5</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.09548135727693899</v>
+        <v>0.06773444830553302</v>
       </c>
       <c r="E70" t="n">
-        <v>0.06888329392167619</v>
+        <v>0.06657906318023601</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.1657 ns</t>
+          <t>0.3090 ns</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H70" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I70" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J70" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K70" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ar.L5</t>
+          <t>ar.L6</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.02643088563834783</v>
+        <v>0.1032258589352957</v>
       </c>
       <c r="E71" t="n">
-        <v>0.06263286860778325</v>
+        <v>0.06694697970197505</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.6730 ns</t>
+          <t>0.1231 ns</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H71" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I71" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J71" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K71" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ar.L6</t>
+          <t>ar.L7</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.04207108520488993</v>
+        <v>-0.3577693040221521</v>
       </c>
       <c r="E72" t="n">
-        <v>0.06888394598065012</v>
+        <v>0.046042162151903</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.5414 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H72" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I72" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J72" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K72" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ARMA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
+          <t>ARMA(7,0) + const on Δ7 log demand  [= ARIMA(7,0,0)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ar.L7</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-0.3803221243236798</v>
+        <v>0.09513254441900669</v>
       </c>
       <c r="E73" t="n">
-        <v>0.06139030377462043</v>
+        <v>0.004507880150999792</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -12581,19 +13561,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>165.3889470634342</v>
+        <v>179.3767394101604</v>
       </c>
       <c r="H73" t="n">
-        <v>210.9780589169605</v>
+        <v>213.5685733003051</v>
       </c>
       <c r="I73" t="n">
-        <v>14737.37333953242</v>
+        <v>13317.70475627446</v>
       </c>
       <c r="J73" t="n">
-        <v>18358.33359956474</v>
+        <v>17853.90132441626</v>
       </c>
       <c r="K73" t="n">
-        <v>57.57383391940481</v>
+        <v>48.08128422960952</v>
       </c>
       <c r="L73" t="inlineStr"/>
     </row>
@@ -12610,18 +13590,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>drift (log/day)</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.5363007935414819</v>
+        <v>0.001674918607212042</v>
       </c>
       <c r="E74" t="n">
-        <v>0.124483478148377</v>
+        <v>0.00236816292397168</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.4794 ns</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12639,7 +13619,11 @@
       <c r="K74" t="n">
         <v>57.57383391940481</v>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Stationary series = seasonal difference of log demand (ADF &amp; KPSS agree, Phase 2). Order chosen by AIC over p≤7, q≤3 (31 candidates). 'drift' is the constant of the Δ7 equation expressed per day. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12654,18 +13638,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ma.L2</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-0.6071494624221841</v>
+        <v>-0.1268547428162264</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1165036738093018</v>
+        <v>0.116969457387242</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.2781 ns</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12698,14 +13682,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ma.L3</t>
+          <t>ar.L2</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.5337200691883398</v>
+        <v>0.7511835494260695</v>
       </c>
       <c r="E76" t="n">
-        <v>0.09275586633865134</v>
+        <v>0.08435763121964718</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -12742,18 +13726,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>ar.L3</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0889223817288141</v>
+        <v>0.2779492326884617</v>
       </c>
       <c r="E77" t="n">
-        <v>0.004759691039512361</v>
+        <v>0.1056935859509285</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0085 **</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12776,336 +13760,332 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>drift (log/day)</t>
+          <t>ar.L4</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.001251444045378105</v>
+        <v>-0.09548135727693899</v>
       </c>
       <c r="E78" t="n">
-        <v>0.005791136784870128</v>
+        <v>0.06888329392167619</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.8289 ns</t>
+          <t>0.1657 ns</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H78" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I78" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J78" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K78" t="n">
-        <v>45.91726426082142</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>auto_arima (exhaustive grid, AIC, KPSS unit-root test chose d=1, non-seasonal, p≤7, q≤3) evaluated 23 candidates; best (7, 1, 1) with intercept=True. Refit in statsmodels ARIMA (trend='t'). Non-seasonal by construction: the weekly cycle can only be absorbed through high-order AR lags. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
-        </is>
-      </c>
+        <v>57.57383391940481</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>ar.L5</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.219527529795834</v>
+        <v>0.02643088563834783</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1338060590290563</v>
+        <v>0.06263286860778325</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.1009 ns</t>
+          <t>0.6730 ns</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H79" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I79" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J79" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K79" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ar.L2</t>
+          <t>ar.L6</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.4099031262185781</v>
+        <v>0.04207108520488993</v>
       </c>
       <c r="E80" t="n">
-        <v>0.09455464233752318</v>
+        <v>0.06888394598065012</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.5414 ns</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H80" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I80" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J80" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K80" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ar.L3</t>
+          <t>ar.L7</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.3162261637244037</v>
+        <v>-0.3803221243236798</v>
       </c>
       <c r="E81" t="n">
-        <v>0.110520974523425</v>
+        <v>0.06139030377462043</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.0042 **</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H81" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I81" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J81" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K81" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ar.L4</t>
+          <t>ma.L1</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-0.3226220061072558</v>
+        <v>0.5363007935414819</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1029538510245724</v>
+        <v>0.124483478148377</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.0017 **</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H82" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I82" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J82" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K82" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ar.L5</t>
+          <t>ma.L2</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-0.3318648477618865</v>
+        <v>-0.6071494624221841</v>
       </c>
       <c r="E83" t="n">
-        <v>0.09602812432814976</v>
+        <v>0.1165036738093018</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.0005 ***</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H83" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I83" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J83" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K83" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ar.L6</t>
+          <t>ma.L3</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.1720490546559557</v>
+        <v>-0.5337200691883398</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1039941879130848</v>
+        <v>0.09275586633865134</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.0980 .</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H84" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I84" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J84" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K84" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>ARMA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
+          <t>ARMA(7,3) + const on Δ7 log demand  [= ARIMA(7,0,3)(0,1,0)7]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ar.L7</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.4488155861287732</v>
+        <v>0.0889223817288141</v>
       </c>
       <c r="E85" t="n">
-        <v>0.07464198530756559</v>
+        <v>0.004759691039512361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -13113,19 +14093,19 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>181.530354011536</v>
+        <v>165.3889470634342</v>
       </c>
       <c r="H85" t="n">
-        <v>219.7014656111681</v>
+        <v>210.9780589169605</v>
       </c>
       <c r="I85" t="n">
-        <v>13265.28655765335</v>
+        <v>14737.37333953242</v>
       </c>
       <c r="J85" t="n">
-        <v>18455.55922268183</v>
+        <v>18358.33359956474</v>
       </c>
       <c r="K85" t="n">
-        <v>45.91726426082142</v>
+        <v>57.57383391940481</v>
       </c>
       <c r="L85" t="inlineStr"/>
     </row>
@@ -13142,18 +14122,18 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>drift (log/day)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.3084043878818273</v>
+        <v>0.001251444045378105</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1439464458010342</v>
+        <v>0.005791136784870128</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.0322 *</t>
+          <t>0.8289 ns</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -13171,7 +14151,11 @@
       <c r="K86" t="n">
         <v>45.91726426082142</v>
       </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>auto_arima (exhaustive grid, AIC, KPSS unit-root test chose d=1, non-seasonal, p≤7, q≤3) evaluated 23 candidates; best (7, 1, 1) with intercept=True. Refit in statsmodels ARIMA (trend='t'). Non-seasonal by construction: the weekly cycle can only be absorbed through high-order AR lags. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13186,18 +14170,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.09303841559043743</v>
+        <v>-0.219527529795834</v>
       </c>
       <c r="E87" t="n">
-        <v>0.005313926474659867</v>
+        <v>0.1338060590290563</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.1009 ns</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -13220,24 +14204,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>ar.L2</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.4431076425581934</v>
+        <v>-0.4099031262185781</v>
       </c>
       <c r="E88" t="n">
-        <v>0.03856863674207678</v>
+        <v>0.09455464233752318</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -13245,359 +14229,351 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>133.8675397506205</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H88" t="n">
-        <v>149.0639103684626</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I88" t="n">
-        <v>9108.629861189735</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J88" t="n">
-        <v>12754.97559384381</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K88" t="n">
-        <v>31.05750751419404</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>d=0, D=1 fixed from Phase 2 (seasonal unit root in ACF). Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. Phase 2 starting model (1,0,0)(0,1,1)7 AIC=140.1; selected AIC=133.9. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
-        </is>
-      </c>
+        <v>45.91726426082142</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ar.S.L7</t>
+          <t>ar.L3</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.3126808545478347</v>
+        <v>-0.3162261637244037</v>
       </c>
       <c r="E89" t="n">
-        <v>0.07578078231709064</v>
+        <v>0.110520974523425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0042 **</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>133.8675397506205</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H89" t="n">
-        <v>149.0639103684626</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I89" t="n">
-        <v>9108.629861189735</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J89" t="n">
-        <v>12754.97559384381</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K89" t="n">
-        <v>31.05750751419404</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ma.S.L7</t>
+          <t>ar.L4</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.8636590714614607</v>
+        <v>-0.3226220061072558</v>
       </c>
       <c r="E90" t="n">
-        <v>0.05731656326480702</v>
+        <v>0.1029538510245724</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0017 **</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>133.8675397506205</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H90" t="n">
-        <v>149.0639103684626</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I90" t="n">
-        <v>9108.629861189735</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J90" t="n">
-        <v>12754.97559384381</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K90" t="n">
-        <v>31.05750751419404</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>ar.L5</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.08415995774562718</v>
+        <v>-0.3318648477618865</v>
       </c>
       <c r="E91" t="n">
-        <v>0.004224512120618054</v>
+        <v>0.09602812432814976</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0005 ***</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>133.8675397506205</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H91" t="n">
-        <v>149.0639103684626</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I91" t="n">
-        <v>9108.629861189735</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J91" t="n">
-        <v>12754.97559384381</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K91" t="n">
-        <v>31.05750751419404</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>dow_Tue</t>
+          <t>ar.L6</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-0.2525898510816694</v>
+        <v>-0.1720490546559557</v>
       </c>
       <c r="E92" t="n">
-        <v>0.08177223910291624</v>
+        <v>0.1039941879130848</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.0020 **</t>
+          <t>0.0980 .</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>54.02949391845218</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H92" t="n">
-        <v>107.469050157937</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I92" t="n">
-        <v>7394.310784885945</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J92" t="n">
-        <v>11220.91902220608</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K92" t="n">
-        <v>28.14532924096643</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Exog: weekday dummies (Mon base), holiday, dec_surge_2023, booknow_missing, lead_100h. d=1, D=0 because seasonal differencing would annihilate the weekday dummies. Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. theater_area not used: this is a single aggregate series, not panel data. USES REALISED LEAD TIME for forecast dates - optimistic/oracle scenario.</t>
-        </is>
-      </c>
+        <v>45.91726426082142</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>dow_Wed</t>
+          <t>ar.L7</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-0.1567162730832398</v>
+        <v>0.4488155861287732</v>
       </c>
       <c r="E93" t="n">
-        <v>0.09412220672938687</v>
+        <v>0.07464198530756559</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.0959 .</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>54.02949391845218</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H93" t="n">
-        <v>107.469050157937</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I93" t="n">
-        <v>7394.310784885945</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J93" t="n">
-        <v>11220.91902220608</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K93" t="n">
-        <v>28.14532924096643</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>dow_Thu</t>
+          <t>ma.L1</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.080371831524768</v>
+        <v>-0.3084043878818273</v>
       </c>
       <c r="E94" t="n">
-        <v>0.09882023632419801</v>
+        <v>0.1439464458010342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.4160 ns</t>
+          <t>0.0322 *</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>54.02949391845218</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H94" t="n">
-        <v>107.469050157937</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I94" t="n">
-        <v>7394.310784885945</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J94" t="n">
-        <v>11220.91902220608</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K94" t="n">
-        <v>28.14532924096643</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>ARIMA(7, 1, 1) trend=t on log demand</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>dow_Fri</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.02591916159349873</v>
+        <v>0.09303841559043743</v>
       </c>
       <c r="E95" t="n">
-        <v>0.09606523630465132</v>
+        <v>0.005313926474659867</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.7873 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>54.02949391845218</v>
+        <v>181.530354011536</v>
       </c>
       <c r="H95" t="n">
-        <v>107.469050157937</v>
+        <v>219.7014656111681</v>
       </c>
       <c r="I95" t="n">
-        <v>7394.310784885945</v>
+        <v>13265.28655765335</v>
       </c>
       <c r="J95" t="n">
-        <v>11220.91902220608</v>
+        <v>18455.55922268183</v>
       </c>
       <c r="K95" t="n">
-        <v>28.14532924096643</v>
+        <v>45.91726426082142</v>
       </c>
       <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>dow_Sat</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.6652343494821126</v>
+        <v>0.4431076425581934</v>
       </c>
       <c r="E96" t="n">
-        <v>0.08614522750491459</v>
+        <v>0.03856863674207678</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -13605,43 +14581,47 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>54.02949391845218</v>
+        <v>133.8675397506205</v>
       </c>
       <c r="H96" t="n">
-        <v>107.469050157937</v>
+        <v>149.0639103684626</v>
       </c>
       <c r="I96" t="n">
-        <v>7394.310784885945</v>
+        <v>9108.629861189735</v>
       </c>
       <c r="J96" t="n">
-        <v>11220.91902220608</v>
+        <v>12754.97559384381</v>
       </c>
       <c r="K96" t="n">
-        <v>28.14532924096643</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>31.05750751419404</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>d=0, D=1 fixed from Phase 2 (seasonal unit root in ACF). Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. Phase 2 starting model (1,0,0)(0,1,1)7 AIC=140.1; selected AIC=133.9. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>dow_Sun</t>
+          <t>ar.S.L7</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.5381846116747208</v>
+        <v>0.3126808545478347</v>
       </c>
       <c r="E97" t="n">
-        <v>0.08896968877398741</v>
+        <v>0.07578078231709064</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -13649,107 +14629,107 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>54.02949391845218</v>
+        <v>133.8675397506205</v>
       </c>
       <c r="H97" t="n">
-        <v>107.469050157937</v>
+        <v>149.0639103684626</v>
       </c>
       <c r="I97" t="n">
-        <v>7394.310784885945</v>
+        <v>9108.629861189735</v>
       </c>
       <c r="J97" t="n">
-        <v>11220.91902220608</v>
+        <v>12754.97559384381</v>
       </c>
       <c r="K97" t="n">
-        <v>28.14532924096643</v>
+        <v>31.05750751419404</v>
       </c>
       <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>is_holiday</t>
+          <t>ma.S.L7</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-0.004625562498806765</v>
+        <v>-0.8636590714614607</v>
       </c>
       <c r="E98" t="n">
-        <v>0.05730929179821688</v>
+        <v>0.05731656326480702</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.9357 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>54.02949391845218</v>
+        <v>133.8675397506205</v>
       </c>
       <c r="H98" t="n">
-        <v>107.469050157937</v>
+        <v>149.0639103684626</v>
       </c>
       <c r="I98" t="n">
-        <v>7394.310784885945</v>
+        <v>9108.629861189735</v>
       </c>
       <c r="J98" t="n">
-        <v>11220.91902220608</v>
+        <v>12754.97559384381</v>
       </c>
       <c r="K98" t="n">
-        <v>28.14532924096643</v>
+        <v>31.05750751419404</v>
       </c>
       <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SARIMAX_with_lead</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+          <t>SARIMA(1, 0, 0)(1, 1, 1, 7) trend=n on log demand</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>dec_surge_2023</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.2952630940019664</v>
+        <v>0.08415995774562718</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1413554578436083</v>
+        <v>0.004224512120618054</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.0367 *</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>54.02949391845218</v>
+        <v>133.8675397506205</v>
       </c>
       <c r="H99" t="n">
-        <v>107.469050157937</v>
+        <v>149.0639103684626</v>
       </c>
       <c r="I99" t="n">
-        <v>7394.310784885945</v>
+        <v>9108.629861189735</v>
       </c>
       <c r="J99" t="n">
-        <v>11220.91902220608</v>
+        <v>12754.97559384381</v>
       </c>
       <c r="K99" t="n">
-        <v>28.14532924096643</v>
+        <v>31.05750751419404</v>
       </c>
       <c r="L99" t="inlineStr"/>
     </row>
@@ -13766,18 +14746,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>booknow_missing</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.02473590949151905</v>
+        <v>-0.2525898510816694</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1190567016387371</v>
+        <v>0.08177223910291624</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.8354 ns</t>
+          <t>0.0020 **</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13795,7 +14775,11 @@
       <c r="K100" t="n">
         <v>28.14532924096643</v>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Exog: weekday dummies (Mon base), holiday, dec_surge_2023, booknow_missing, lead_100h. d=1, D=0 because seasonal differencing would annihilate the weekday dummies. Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. theater_area not used: this is a single aggregate series, not panel data. USES REALISED LEAD TIME for forecast dates - optimistic/oracle scenario.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13810,18 +14794,18 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>lead_100h</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.3407903156906337</v>
+        <v>-0.1567162730832398</v>
       </c>
       <c r="E101" t="n">
-        <v>0.01386555648511848</v>
+        <v>0.09412220672938687</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0959 .</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13854,18 +14838,18 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.3594013269416433</v>
+        <v>0.080371831524768</v>
       </c>
       <c r="E102" t="n">
-        <v>0.04766674759164532</v>
+        <v>0.09882023632419801</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.4160 ns</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13898,18 +14882,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.9739130331536426</v>
+        <v>0.02591916159349873</v>
       </c>
       <c r="E103" t="n">
-        <v>0.01570854783155902</v>
+        <v>0.09606523630465132</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.7873 ns</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13942,14 +14926,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ar.S.L7</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.3975027951175682</v>
+        <v>0.6652343494821126</v>
       </c>
       <c r="E104" t="n">
-        <v>0.04012565832374835</v>
+        <v>0.08614522750491459</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13986,14 +14970,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>dow_Sun</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.06276712611478745</v>
+        <v>0.5381846116747208</v>
       </c>
       <c r="E105" t="n">
-        <v>0.003474208072702667</v>
+        <v>0.08896968877398741</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -14020,7 +15004,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -14030,45 +15014,41 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>dow_Tue</t>
+          <t>is_holiday</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-0.3152199004155812</v>
+        <v>-0.004625562498806765</v>
       </c>
       <c r="E106" t="n">
-        <v>0.09638080251684168</v>
+        <v>0.05730929179821688</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0.0011 **</t>
+          <t>0.9357 ns</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H106" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I106" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J106" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K106" t="n">
-        <v>37.29118892550915</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Exog: weekday dummies (Mon base), holiday, dec_surge_2023, booknow_missing. d=1, D=0 because seasonal differencing would annihilate the weekday dummies. Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. theater_area not used: this is a single aggregate series, not panel data.</t>
-        </is>
-      </c>
+        <v>28.14532924096643</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -14078,41 +15058,41 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>dow_Wed</t>
+          <t>dec_surge_2023</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-0.2282391960361606</v>
+        <v>0.2952630940019664</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1033873285158144</v>
+        <v>0.1413554578436083</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0.0273 *</t>
+          <t>0.0367 *</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H107" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I107" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J107" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K107" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -14122,41 +15102,41 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>dow_Thu</t>
+          <t>booknow_missing</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.04059572706269917</v>
+        <v>-0.02473590949151905</v>
       </c>
       <c r="E108" t="n">
-        <v>0.108160400970815</v>
+        <v>0.1190567016387371</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0.7074 ns</t>
+          <t>0.8354 ns</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H108" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I108" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J108" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K108" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -14166,41 +15146,41 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>dow_Fri</t>
+          <t>lead_100h</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.01572062768220071</v>
+        <v>0.3407903156906337</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1059956490529578</v>
+        <v>0.01386555648511848</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0.8821 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H109" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I109" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J109" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K109" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -14210,14 +15190,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>dow_Sat</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.7235083564229734</v>
+        <v>0.3594013269416433</v>
       </c>
       <c r="E110" t="n">
-        <v>0.09240823646223252</v>
+        <v>0.04766674759164532</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14225,26 +15205,26 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H110" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I110" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J110" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K110" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -14254,14 +15234,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>dow_Sun</t>
+          <t>ma.L1</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.6684581435161542</v>
+        <v>-0.9739130331536426</v>
       </c>
       <c r="E111" t="n">
-        <v>0.09258755571298309</v>
+        <v>0.01570854783155902</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14269,26 +15249,26 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H111" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I111" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J111" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K111" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -14298,41 +15278,41 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>is_holiday</t>
+          <t>ar.S.L7</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.0250502652676293</v>
+        <v>0.3975027951175682</v>
       </c>
       <c r="E112" t="n">
-        <v>0.06268793348514635</v>
+        <v>0.04012565832374835</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.6894 ns</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H112" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I112" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J112" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K112" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SARIMAX_no_lead</t>
+          <t>SARIMAX_with_lead</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -14342,34 +15322,34 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>dec_surge_2023</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.284872777718891</v>
+        <v>0.06276712611478745</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1522781761872198</v>
+        <v>0.003474208072702667</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0.0614 .</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>127.2747055697288</v>
+        <v>54.02949391845218</v>
       </c>
       <c r="H113" t="n">
-        <v>176.8971506492504</v>
+        <v>107.469050157937</v>
       </c>
       <c r="I113" t="n">
-        <v>7552.243223539159</v>
+        <v>7394.310784885945</v>
       </c>
       <c r="J113" t="n">
-        <v>9283.570749349237</v>
+        <v>11220.91902220608</v>
       </c>
       <c r="K113" t="n">
-        <v>37.29118892550915</v>
+        <v>28.14532924096643</v>
       </c>
       <c r="L113" t="inlineStr"/>
     </row>
@@ -14386,18 +15366,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>booknow_missing</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-0.01959732730632385</v>
+        <v>-0.3152199004155812</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1401090927053232</v>
+        <v>0.09638080251684168</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>0.8888 ns</t>
+          <t>0.0011 **</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14415,7 +15395,11 @@
       <c r="K114" t="n">
         <v>37.29118892550915</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Exog: weekday dummies (Mon base), holiday, dec_surge_2023, booknow_missing. d=1, D=0 because seasonal differencing would annihilate the weekday dummies. Grid p,q≤2, P,Q≤1, trend n/t (72 fits) by AIC. theater_area not used: this is a single aggregate series, not panel data.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14430,18 +15414,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.4038456073277222</v>
+        <v>-0.2282391960361606</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04882660514367867</v>
+        <v>0.1033873285158144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.0273 *</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14474,18 +15458,18 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-0.9538872208388846</v>
+        <v>0.04059572706269917</v>
       </c>
       <c r="E116" t="n">
-        <v>0.01589542084054867</v>
+        <v>0.108160400970815</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.7074 ns</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14518,18 +15502,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ar.S.L7</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.4224240458201703</v>
+        <v>0.01572062768220071</v>
       </c>
       <c r="E117" t="n">
-        <v>0.04273112536115059</v>
+        <v>0.1059956490529578</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>0.0000 ***</t>
+          <t>0.8821 ns</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14562,14 +15546,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.07861143542256209</v>
+        <v>0.7235083564229734</v>
       </c>
       <c r="E118" t="n">
-        <v>0.004476644796697782</v>
+        <v>0.09240823646223252</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14592,6 +15576,358 @@
         <v>37.29118892550915</v>
       </c>
       <c r="L118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>dow_Sun</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6684581435161542</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.09258755571298309</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H119" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I119" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J119" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K119" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>is_holiday</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>-0.0250502652676293</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.06268793348514635</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0.6894 ns</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H120" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I120" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J120" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K120" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>dec_surge_2023</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.284872777718891</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1522781761872198</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0.0614 .</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H121" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I121" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J121" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K121" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>booknow_missing</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.01959732730632385</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.1401090927053232</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0.8888 ns</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H122" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I122" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J122" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K122" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ar.L1</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.4038456073277222</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.04882660514367867</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H123" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I123" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J123" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K123" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ma.L1</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.9538872208388846</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.01589542084054867</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H124" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I124" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J124" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K124" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ar.S.L7</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.4224240458201703</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.04273112536115059</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H125" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I125" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J125" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K125" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SARIMAX_no_lead</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SARIMAX(1, 1, 1)(1, 0, 0, 7) trend=n + exog on log demand</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sigma2</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.07861143542256209</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.004476644796697782</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0.0000 ***</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>127.2747055697288</v>
+      </c>
+      <c r="H126" t="n">
+        <v>176.8971506492504</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7552.243223539159</v>
+      </c>
+      <c r="J126" t="n">
+        <v>9283.570749349237</v>
+      </c>
+      <c r="K126" t="n">
+        <v>37.29118892550915</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17002,7 +18338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17022,7 +18358,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>MLR_with_lead — inference table (validation metrics: Jan 2024, multi-step)</t>
+          <t>Trend_Dummy_Reg — inference table (validation metrics: Jan 2024, multi-step)</t>
         </is>
       </c>
     </row>
@@ -17091,12 +18427,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17105,10 +18441,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.696240178688386</v>
+        <v>9.300356922356313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7168212747589217</v>
+        <v>0.07428650903424695</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17116,719 +18452,499 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H3" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I3" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J3" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K3" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OLS on log demand, HAC(7) standard errors. Recursive multi-step forecast. Interval is an approximation (residual sd × sqrt(min(h,7))). USES REALISED LEAD TIME for forecast dates (information not available in advance) - optimistic/oracle scenario.</t>
+          <t>Trend + seasonal-dummy regression on log demand (exp(coef) = multiplier vs Monday). No lags, so residual autocorrelation is expected; HAC(7) standard errors. Fitted on December-adjusted demand: Dec 2023 divided by the surge multiplier 2.50x (OLS dummy on train, p=1e-08); forecasts are for normal (non-surge) conditions.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lag1_log_demand</t>
+          <t>trend_month</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1967654320199931</v>
+        <v>0.02960393764688295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09784578666994671</v>
+        <v>0.00998812775251692</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0443 *</t>
+          <t>0.0030 **</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H4" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I4" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J4" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K4" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lag7_log_demand</t>
+          <t>dow_Tue</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3179456114877093</v>
+        <v>-0.3244542000400762</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07934494859968066</v>
+        <v>0.0476166389251341</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0001 ***</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H5" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I5" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J5" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K5" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dow_Tue</t>
+          <t>dow_Wed</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.009367935580455927</v>
+        <v>-0.2319086230854109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05787834148776607</v>
+        <v>0.07086703161902613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.8714 ns</t>
+          <t>0.0011 **</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H6" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I6" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J6" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K6" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dow_Wed</t>
+          <t>dow_Thu</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.149087255613652</v>
+        <v>0.037557561004528</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09451253528506465</v>
+        <v>0.07475173495063558</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.1147 ns</t>
+          <t>0.6154 ns</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H7" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I7" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J7" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K7" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dow_Thu</t>
+          <t>dow_Fri</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2862472886603507</v>
+        <v>-0.003116878632527642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09708820071458177</v>
+        <v>0.07208266541889143</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0032 **</t>
+          <t>0.9655 ns</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H8" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I8" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J8" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K8" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dow_Fri</t>
+          <t>dow_Sat</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1761451594528244</v>
+        <v>0.7235793767118635</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05964930279107389</v>
+        <v>0.09320822091908157</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0031 **</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H9" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I9" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J9" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K9" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
+          <t>Trend_Dummy_Reg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
+          <t>OLS: const + linear trend + weekday dummies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dow_Sat</t>
+          <t>dow_Sun</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6093423269863116</v>
+        <v>0.676017892445303</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1574562723983261</v>
+        <v>0.06105984446324666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0001 ***</t>
+          <t>0.0000 ***</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>16.2116785128743</v>
+        <v>224.886106476582</v>
       </c>
       <c r="H10" t="n">
-        <v>65.59988302086113</v>
+        <v>255.4467699194009</v>
       </c>
       <c r="I10" t="n">
-        <v>9167.306312588355</v>
+        <v>7000.529711986843</v>
       </c>
       <c r="J10" t="n">
-        <v>12516.99275536766</v>
+        <v>10147.42859892897</v>
       </c>
       <c r="K10" t="n">
-        <v>36.28102722777211</v>
+        <v>23.09984953203552</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MLR_with_lead</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dow_Sun</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.3171253249757077</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.09816353733158333</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.0012 **</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>16.2116785128743</v>
-      </c>
-      <c r="H11" t="n">
-        <v>65.59988302086113</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9167.306312588355</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12516.99275536766</v>
-      </c>
-      <c r="K11" t="n">
-        <v>36.28102722777211</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MLR_with_lead</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>is_holiday</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.01264020421706977</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.05017640757805472</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.8011 ns</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>16.2116785128743</v>
-      </c>
-      <c r="H12" t="n">
-        <v>65.59988302086113</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9167.306312588355</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12516.99275536766</v>
-      </c>
-      <c r="K12" t="n">
-        <v>36.28102722777211</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MLR_with_lead</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dec_surge_2023</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1840496799769273</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1334841640408609</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.1680 ns</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>16.2116785128743</v>
-      </c>
-      <c r="H13" t="n">
-        <v>65.59988302086113</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9167.306312588355</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12516.99275536766</v>
-      </c>
-      <c r="K13" t="n">
-        <v>36.28102722777211</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Residual diagnostics (in-sample, train)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MLR_with_lead</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>booknow_missing</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.03805524728166586</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.03200316502979435</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.2344 ns</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>16.2116785128743</v>
-      </c>
-      <c r="H14" t="n">
-        <v>65.59988302086113</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9167.306312588355</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12516.99275536766</v>
-      </c>
-      <c r="K14" t="n">
-        <v>36.28102722777211</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MLR_with_lead</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>OLS: lag1, lag7, weekday dummies, holiday, dec_surge, booknow_missing, lead</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>lead_100h</t>
-        </is>
+          <t>Ljung-Box lag 7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>112.3112289060696</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.042623308602648e-21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3562186524960662</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1698309457411886</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.0360 *</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>16.2116785128743</v>
-      </c>
-      <c r="H15" t="n">
-        <v>65.59988302086113</v>
-      </c>
-      <c r="I15" t="n">
-        <v>9167.306312588355</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12516.99275536766</v>
-      </c>
-      <c r="K15" t="n">
-        <v>36.28102722777211</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>autocorrelation left</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ljung-Box lag 14</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>122.2003782772988</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.330839206710618e-19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>autocorrelation left</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ljung-Box lag 21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>137.7945033858223</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.549733576877267e-19</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>autocorrelation left</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Residual diagnostics (in-sample, train)</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jarque-Bera normality</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>123.766402532796</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.331886348383204e-27</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>non-normal</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>verdict</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shapiro-Wilk normality</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9463759303183992</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.028266365466689e-09</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>non-normal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ljung-Box lag 7</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.206945207311039</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.1010890987915266</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>residuals white noise</t>
-        </is>
-      </c>
+        <v>0.2658282403615451</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ljung-Box lag 14</t>
+          <t>excess kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.53133842338016</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.02353916574718243</v>
-      </c>
-      <c r="D21" t="n">
-        <v>12</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>autocorrelation left</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Ljung-Box lag 21</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>29.74160845500177</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.05518036044962926</v>
-      </c>
-      <c r="D22" t="n">
-        <v>19</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>residuals white noise</t>
-        </is>
-      </c>
+        <v>2.920884437841818</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Jarque-Bera normality</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>855.5116478636742</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.69046453687632e-186</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>non-normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Shapiro-Wilk normality</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.8951222792615157</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2.635095636036399e-14</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>non-normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>skewness</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-0.6997142241938138</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>excess kurtosis</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>7.762771989011615</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Residual plot, ACF and Q-Q</t>
         </is>
